--- a/public/excel/遂川县十三五非贫困村25户以上自然村通水泥路建设计划项目表（已列交通口计划未实施）.xlsx
+++ b/public/excel/遂川县十三五非贫困村25户以上自然村通水泥路建设计划项目表（已列交通口计划未实施）.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58">
   <si>
     <t>遂川县十三五非贫困村25户以上自然村通水泥路建设计划项目表（已列交通口计划未实施）</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>本次拨入</t>
+  </si>
+  <si>
+    <t>已经支付</t>
   </si>
   <si>
     <t>备注</t>
@@ -194,11 +197,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -254,6 +257,117 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -262,48 +376,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -314,95 +406,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -413,49 +416,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,78 +566,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -557,30 +590,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -588,12 +597,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,34 +676,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -720,17 +720,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -755,17 +764,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -777,10 +780,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -789,139 +792,139 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1347,7 +1350,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
@@ -1364,8 +1367,8 @@
     <col min="12" max="12" width="6.875" style="5" customWidth="1"/>
     <col min="13" max="13" width="7.125" customWidth="1"/>
     <col min="14" max="14" width="13.5" customWidth="1"/>
-    <col min="15" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="14.875" customWidth="1"/>
+    <col min="15" max="17" width="10.125" customWidth="1"/>
+    <col min="18" max="18" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:1">
@@ -1373,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="69" customHeight="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" ht="69" customHeight="1" spans="1:18">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1425,11 +1428,14 @@
       <c r="Q2" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="R2" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="24" customHeight="1" outlineLevel="1" spans="1:17">
+    <row r="3" s="2" customFormat="1" ht="24" customHeight="1" outlineLevel="1" spans="1:18">
       <c r="A3" s="8"/>
       <c r="B3" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1454,11 +1460,12 @@
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="8"/>
     </row>
-    <row r="4" s="3" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="4" s="3" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A4" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="13"/>
@@ -1484,27 +1491,28 @@
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="24"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="24"/>
     </row>
-    <row r="5" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="5" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A5" s="14">
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="14">
         <v>25</v>
@@ -1513,10 +1521,10 @@
         <v>86</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" s="14">
         <v>3</v>
@@ -1533,34 +1541,35 @@
         <v>60</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P5" s="14">
         <v>33.864</v>
       </c>
-      <c r="Q5" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="R5"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5"/>
     </row>
-    <row r="6" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="6" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A6" s="14">
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="14">
         <v>118</v>
@@ -1569,10 +1578,10 @@
         <v>389</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K6" s="14">
         <v>2.7</v>
@@ -1589,37 +1598,40 @@
         <v>67.5</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P6" s="14">
         <v>38.097</v>
       </c>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="26"/>
+      <c r="Q6" s="14">
+        <v>38.097</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="26"/>
     </row>
-    <row r="7" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="7" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A7" s="14">
         <v>3</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15">
@@ -1636,37 +1648,38 @@
         <v>13.3</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P7" s="14">
         <v>7.5065</v>
       </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="26"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="26"/>
     </row>
-    <row r="8" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="8" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A8" s="14">
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15">
@@ -1683,37 +1696,38 @@
         <v>21</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" s="14">
         <v>11.8524</v>
       </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="26"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="26"/>
     </row>
-    <row r="9" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="9" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A9" s="14">
         <v>5</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15">
@@ -1730,37 +1744,38 @@
         <v>7</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P9" s="14">
         <v>3.9508</v>
       </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="26"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="26"/>
     </row>
-    <row r="10" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="10" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A10" s="14">
         <v>6</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
       <c r="I10" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15">
@@ -1777,37 +1792,40 @@
         <v>18</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P10" s="14">
         <v>10.1592</v>
       </c>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="26"/>
+      <c r="Q10" s="14">
+        <v>9</v>
+      </c>
+      <c r="R10" s="15"/>
+      <c r="S10" s="26"/>
     </row>
-    <row r="11" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="11" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A11" s="14">
         <v>7</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
       <c r="I11" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15">
@@ -1824,37 +1842,40 @@
         <v>30</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P11" s="14">
         <v>16.932</v>
       </c>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="26"/>
+      <c r="Q11" s="14">
+        <v>15</v>
+      </c>
+      <c r="R11" s="15"/>
+      <c r="S11" s="26"/>
     </row>
-    <row r="12" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="12" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A12" s="14">
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15">
@@ -1871,32 +1892,35 @@
         <v>21</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P12" s="14">
         <v>11.8524</v>
       </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="26"/>
+      <c r="Q12" s="14">
+        <v>11</v>
+      </c>
+      <c r="R12" s="15"/>
+      <c r="S12" s="26"/>
     </row>
-    <row r="13" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="13" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A13" s="14">
         <v>9</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="18">
         <v>46</v>
@@ -1905,10 +1929,10 @@
         <v>155</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K13" s="16">
         <v>0.8</v>
@@ -1924,32 +1948,33 @@
         <v>16</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P13" s="14">
         <v>9.0304</v>
       </c>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="26"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="26"/>
     </row>
-    <row r="14" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:18">
+    <row r="14" s="4" customFormat="1" ht="24" customHeight="1" outlineLevel="2" spans="1:19">
       <c r="A14" s="14">
         <v>11</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="14">
         <v>40</v>
@@ -1958,10 +1983,10 @@
         <v>135</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K14" s="14">
         <v>0.8</v>
@@ -1978,21 +2003,22 @@
         <v>16</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P14" s="14">
         <v>9.0304</v>
       </c>
-      <c r="Q14" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="R14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="S14"/>
     </row>
     <row r="15" ht="20.25" customHeight="1"/>
     <row r="16" ht="20.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/excel/遂川县十三五非贫困村25户以上自然村通水泥路建设计划项目表（已列交通口计划未实施）.xlsx
+++ b/public/excel/遂川县十三五非贫困村25户以上自然村通水泥路建设计划项目表（已列交通口计划未实施）.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23895" windowHeight="10350"/>
+    <workbookView windowWidth="23895" windowHeight="9930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="0.001"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -197,10 +197,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
   <fonts count="29">
@@ -257,6 +257,87 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -265,62 +346,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -331,24 +356,17 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -360,6 +378,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -376,35 +401,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -416,187 +416,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,21 +675,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -720,26 +705,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -759,7 +744,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -767,8 +752,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,10 +780,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -792,139 +792,139 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1546,7 +1546,9 @@
       <c r="P5" s="14">
         <v>33.864</v>
       </c>
-      <c r="Q5" s="14"/>
+      <c r="Q5" s="14">
+        <v>30</v>
+      </c>
       <c r="R5" s="25" t="s">
         <v>29</v>
       </c>
@@ -1653,7 +1655,9 @@
       <c r="P7" s="14">
         <v>7.5065</v>
       </c>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="14">
+        <v>7.5</v>
+      </c>
       <c r="R7" s="15"/>
       <c r="S7" s="26"/>
     </row>
@@ -1701,7 +1705,9 @@
       <c r="P8" s="14">
         <v>11.8524</v>
       </c>
-      <c r="Q8" s="14"/>
+      <c r="Q8" s="14">
+        <v>11.5</v>
+      </c>
       <c r="R8" s="15"/>
       <c r="S8" s="26"/>
     </row>
@@ -1749,7 +1755,10 @@
       <c r="P9" s="14">
         <v>3.9508</v>
       </c>
-      <c r="Q9" s="14"/>
+      <c r="Q9" s="14">
+        <f>+P9</f>
+        <v>3.9508</v>
+      </c>
       <c r="R9" s="15"/>
       <c r="S9" s="26"/>
     </row>
@@ -2008,7 +2017,10 @@
       <c r="P14" s="14">
         <v>9.0304</v>
       </c>
-      <c r="Q14" s="14"/>
+      <c r="Q14" s="14">
+        <f>+P14</f>
+        <v>9.0304</v>
+      </c>
       <c r="R14" s="25" t="s">
         <v>57</v>
       </c>
